--- a/output/第10期計画_地域差の分析.xlsx
+++ b/output/第10期計画_地域差の分析.xlsx
@@ -6935,7 +6935,7 @@
     <row r="28" ht="110" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>注1）6区分平均は、算定できる区分の単純平均である。区分ごとの給付額が異なるため、給付額による加重平均とは一致しない。東川町・東神楽町は多機能系が算定できないため5区分の平均である。注2）3町のなかで自給率が最も高いのは美瑛町（77.5％）、最も低いのは東神楽町（63.2％）である。東神楽町は面積68.5km²で旭川市に隣接しており、区域外（旭川市）の事業所を利用しやすい条件にある。注3）「その他」の区分には、福祉用具貸与、居宅療養管理指導、特定施設入居者生活介護以外の居宅サービス等が含まれる。区域内に事業所が存在しないサービスが28種別中11種別あることと整合する。</t>
+          <t>注1）6区分平均は、算定できる区分の単純平均である。区分ごとの給付額が異なるため、給付額による加重平均とは一致しない。東川町・東神楽町は多機能系が算定できないため5区分の平均である。注2）3町のなかで自給率が最も高いのは美瑛町（77.5％）、最も低いのは東神楽町（63.2％）である。東神楽町は面積68.5km²で旭川市に隣接しており、区域外（旭川市）の事業所を利用しやすい条件にある。注3）「その他」の区分には、福祉用具貸与、居宅療養管理指導、特定施設入居者生活介護以外の居宅サービス等が含まれる。区域内に事業所が存在しないサービスが28種別中11種別あることと符合する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_地域差の分析.xlsx
+++ b/output/第10期計画_地域差の分析.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>6区分平均は美瑛77.5％・東川67.1％・東神楽63.2％。訪問系では東川が管内2位と高い一方、「その他」は3町とも43〜51％にとどまる。</t>
+          <t>算定可能区分の単純平均（美瑛6区分、東川・東神楽5区分）は美瑛77.5％・東川67.1％・東神楽63.2％。訪問系では東川が管内2位と高い一方、「その他」は3町とも43〜51％にとどまる。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「主張の根拠水準の棚卸しと再レビュー」で E4（推論）・E5（仮説）と分類した主張のうち、自給率により水準が変わるものを示す。</t>
+          <t>受託者の自己点検で E4（推論）・E5（仮説）と分類した主張のうち、自給率により水準が変わるものを示す。</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
     <row r="20" ht="110" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>注1）自給率の受領により、水準が上がったのはD5の1件である。仮説（E5）から一次データによる算定（E2）へ引き上げられた。同時に、D5に含まれていた「給付水準の高さの原因」という部分は関係が確認できず、記述しないこととした。1つの主張が、確定した部分と否定された部分に分かれた例である。注2）C1・C2は水準が変わらないが、按分の記述を撤回する点でより強い制約がかかった。自給率を得たことにより主張が弱まった例である。資料の受領は必ず主張を強めるとは限らない。注3）新たに追加する主張5件を含め、「主張の根拠水準の棚卸しと再レビュー」01シートの主張は46件から51件となる。</t>
+          <t>注1）自給率の受領により、水準が上がったのはD5の1件である。仮説（E5）から一次データによる算定（E2）へ引き上げられた。同時に、D5に含まれていた「給付水準の高さの原因」という部分は関係が確認できず、記述しないこととした。1つの主張が、確定した部分と否定された部分に分かれた例である。注2）C1・C2は水準が変わらないが、按分の記述を撤回する点でより強い制約がかかった。自給率を得たことにより主張が弱まった例である。資料の受領は必ず主張を強めるとは限らない。注3）新たに追加する主張5件を含め、受託者の自己点検における主張は46件から51件となる。</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「主張の根拠水準の棚卸しと再レビュー」で E4・E5 と分類した財政（H領域）の主張のうち、C1により水準が変わるものを示す。</t>
+          <t>受託者の自己点検で E4・E5 と分類した財政（H領域）の主張のうち、C1により水準が変わるものを示す。</t>
         </is>
       </c>
     </row>
